--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS CON MEDICION 4 INDICADORES/4 indicadores.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS CON MEDICION 4 INDICADORES/4 indicadores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS CON MEDICION 4 INDICADORES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AGS\DESARROLLO\GITHUB\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS CON MEDICION 4 INDICADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AECBA4-0321-4A29-B8DB-33E2D139FFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510F2B51-238B-4D6D-964C-AE3C3C931481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -30,16 +30,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>campoa</t>
   </si>
@@ -104,23 +105,47 @@
     <t>20.04.2026</t>
   </si>
   <si>
-    <t>0259-2022</t>
-  </si>
-  <si>
-    <t>0411-2021</t>
-  </si>
-  <si>
-    <t>FUNDACION CLINICA LETICIA</t>
-  </si>
-  <si>
-    <t>HOSPITAL FEDERICO LLERAS ACOSTA E.S.E.</t>
+    <t>0280-2022</t>
+  </si>
+  <si>
+    <t>0984-2021</t>
+  </si>
+  <si>
+    <t>0920-2024</t>
+  </si>
+  <si>
+    <t>0905-2021</t>
+  </si>
+  <si>
+    <t>0124-2026</t>
+  </si>
+  <si>
+    <t>0561-2024</t>
+  </si>
+  <si>
+    <t>ESE SOR TERESA ADELE</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO SALUD PEREIRA</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL SAN ANTONIO DE SESQUILE</t>
+  </si>
+  <si>
+    <t>E.S.E. CENTRO DE SALUD DE TAUSA</t>
+  </si>
+  <si>
+    <t>CLÍNICA OSPEDALE MANIZALES S.A</t>
+  </si>
+  <si>
+    <t>PARAMEDICOS S A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,16 +153,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -145,17 +187,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,19 +566,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}">
-  <dimension ref="A1:T3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="11.42578125" style="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="11.375" style="1"/>
+    <col min="13" max="13" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="11.375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -563,109 +638,111 @@
       </c>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="120" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="85.5">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="F2" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="G2" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="H2" s="1">
-        <v>5</v>
+      <c r="E2" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3">
+        <v>4</v>
       </c>
       <c r="I2" s="1">
+        <f>AVERAGE(E2:H2)</f>
         <v>4</v>
       </c>
-      <c r="J2" s="1">
-        <v>68</v>
+      <c r="J2" s="4">
+        <v>24</v>
       </c>
       <c r="K2" s="1">
         <f>J2/2</f>
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="L2" s="1">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="M2" s="2" t="str">
-        <f t="shared" ref="M2:M3" si="0">IF(E2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <f t="shared" ref="M2:M7" si="0">IF(E2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
         <v>cumplimiento del indicador</v>
       </c>
       <c r="N2" s="2" t="str">
-        <f t="shared" ref="N2:N3" si="1">IF(F2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <f t="shared" ref="N2:N7" si="1">IF(F2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
         <v>cumplimiento del indicador</v>
       </c>
       <c r="O2" s="2" t="str">
-        <f t="shared" ref="O2:O3" si="2">IF(G2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <f t="shared" ref="O2:O7" si="2">IF(G2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
         <v>cumplimiento del indicador</v>
       </c>
       <c r="P2" s="2" t="str">
-        <f t="shared" ref="P2:P3" si="3">IF(H2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <f t="shared" ref="P2:P7" si="3">IF(H2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
         <v>cumplimiento del indicador</v>
       </c>
       <c r="Q2" s="2" t="str">
-        <f t="shared" ref="Q2:Q3" si="4">IF(I2&gt;=4,"Cumplimiento en la evaluación de los indicadores.","No cumplimiento en la evaluación de los indicadores.")</f>
+        <f t="shared" ref="Q2:Q7" si="4">IF(I2&gt;=4,"Cumplimiento en la evaluación de los indicadores.","No cumplimiento en la evaluación de los indicadores.")</f>
         <v>Cumplimiento en la evaluación de los indicadores.</v>
       </c>
       <c r="R2" s="2" t="str">
-        <f t="shared" ref="R2:R3" si="5">IF(I2&gt;=4,"no se requiere plan de mejora","Se requiere plan de mejora.")</f>
+        <f t="shared" ref="R2:R7" si="5">IF(I2&gt;=4,"no se requiere plan de mejora","Se requiere plan de mejora.")</f>
         <v>no se requiere plan de mejora</v>
       </c>
       <c r="S2" s="2" t="str">
-        <f t="shared" ref="S2:S3" si="6">IF(I2&gt;=4,"se evidencia cumplimiento en la evaluacion de los indicadores","se evidencia incumplimiento en la evaluacion de los indicadores")</f>
+        <f t="shared" ref="S2:S7" si="6">IF(I2&gt;=4,"se evidencia cumplimiento en la evaluacion de los indicadores","se evidencia incumplimiento en la evaluacion de los indicadores")</f>
         <v>se evidencia cumplimiento en la evaluacion de los indicadores</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="85.5">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="F3" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="G3" s="1">
-        <v>5</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="E3" s="3">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3">
         <v>5</v>
       </c>
       <c r="I3" s="1">
-        <v>4</v>
-      </c>
-      <c r="J3" s="1">
-        <v>103</v>
+        <f t="shared" ref="I3:I7" si="7">AVERAGE(E3:H3)</f>
+        <v>5</v>
+      </c>
+      <c r="J3" s="4">
+        <v>13</v>
       </c>
       <c r="K3" s="1">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="L3" s="1">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="M3" s="2" t="str">
         <f t="shared" si="0"/>
@@ -692,6 +769,277 @@
         <v>no se requiere plan de mejora</v>
       </c>
       <c r="S3" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>se evidencia cumplimiento en la evaluacion de los indicadores</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="85.5">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5</v>
+      </c>
+      <c r="F4" s="3">
+        <v>5</v>
+      </c>
+      <c r="G4" s="3">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3">
+        <v>5</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="J4" s="4">
+        <v>29</v>
+      </c>
+      <c r="K4" s="1">
+        <v>13</v>
+      </c>
+      <c r="L4" s="1">
+        <v>14</v>
+      </c>
+      <c r="M4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="N4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="P4" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="Q4" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="R4" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>no se requiere plan de mejora</v>
+      </c>
+      <c r="S4" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>se evidencia cumplimiento en la evaluacion de los indicadores</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="85.5">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3">
+        <v>5</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3">
+        <v>5</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="J5" s="4">
+        <v>22</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" ref="K5:K7" si="8">J5/2</f>
+        <v>11</v>
+      </c>
+      <c r="L5" s="1">
+        <v>11</v>
+      </c>
+      <c r="M5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="N5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="O5" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="P5" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="Q5" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="R5" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>no se requiere plan de mejora</v>
+      </c>
+      <c r="S5" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>se evidencia cumplimiento en la evaluacion de los indicadores</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="85.5">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3">
+        <v>5</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="J6" s="4">
+        <v>20</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="L6" s="1">
+        <v>10</v>
+      </c>
+      <c r="M6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="N6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="O6" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="P6" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="Q6" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="R6" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>no se requiere plan de mejora</v>
+      </c>
+      <c r="S6" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>se evidencia cumplimiento en la evaluacion de los indicadores</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="85.5">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3">
+        <v>5</v>
+      </c>
+      <c r="H7" s="3">
+        <v>5</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="J7" s="4">
+        <v>28</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="L7" s="1">
+        <v>14</v>
+      </c>
+      <c r="M7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="N7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="O7" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="P7" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="Q7" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="R7" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>no se requiere plan de mejora</v>
+      </c>
+      <c r="S7" s="2" t="str">
         <f t="shared" si="6"/>
         <v>se evidencia cumplimiento en la evaluacion de los indicadores</v>
       </c>
